--- a/data/auto-loan.xlsx
+++ b/data/auto-loan.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -439,38 +439,9 @@
         <v>notes</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>tesla-loan</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Tesla Model 3 Loan</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Fixed 60mo</v>
-      </c>
-      <c r="D2">
-        <v>30000</v>
-      </c>
-      <c r="E2">
-        <v>22400</v>
-      </c>
-      <c r="F2">
-        <v>4.99</v>
-      </c>
-      <c r="G2">
-        <v>566</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2029-01-15</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Tesla financing. $8K down payment.</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/auto-loan.xlsx
+++ b/data/auto-loan.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I3"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -439,9 +439,67 @@
         <v>notes</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>tesla-loan</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Tesla Model Y Loan</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Fixed 60mo</v>
+      </c>
+      <c r="D2">
+        <v>42000</v>
+      </c>
+      <c r="E2">
+        <v>35000</v>
+      </c>
+      <c r="F2">
+        <v>5.49</v>
+      </c>
+      <c r="G2">
+        <v>805</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2029-03-15</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Tesla financing. $16K down payment.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>bmw-loan</v>
+      </c>
+      <c r="B3" t="str">
+        <v>BMW X3 Loan</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Fixed 60mo</v>
+      </c>
+      <c r="D3">
+        <v>40000</v>
+      </c>
+      <c r="E3">
+        <v>28000</v>
+      </c>
+      <c r="F3">
+        <v>4.99</v>
+      </c>
+      <c r="G3">
+        <v>755</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2028-06-01</v>
+      </c>
+      <c r="I3" t="str">
+        <v>BMW Financial Services. $12K down payment.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/auto-loan.xlsx
+++ b/data/auto-loan.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I1"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -439,67 +439,9 @@
         <v>notes</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>tesla-loan</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Tesla Model Y Loan</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Fixed 60mo</v>
-      </c>
-      <c r="D2">
-        <v>42000</v>
-      </c>
-      <c r="E2">
-        <v>35000</v>
-      </c>
-      <c r="F2">
-        <v>5.49</v>
-      </c>
-      <c r="G2">
-        <v>805</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2029-03-15</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Tesla financing. $16K down payment.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>bmw-loan</v>
-      </c>
-      <c r="B3" t="str">
-        <v>BMW X3 Loan</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Fixed 60mo</v>
-      </c>
-      <c r="D3">
-        <v>40000</v>
-      </c>
-      <c r="E3">
-        <v>28000</v>
-      </c>
-      <c r="F3">
-        <v>4.99</v>
-      </c>
-      <c r="G3">
-        <v>755</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2028-06-01</v>
-      </c>
-      <c r="I3" t="str">
-        <v>BMW Financial Services. $12K down payment.</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
   </ignoredErrors>
 </worksheet>
 </file>